--- a/apps/server/test/fixtures/fall-2026-sample.xlsx
+++ b/apps/server/test/fixtures/fall-2026-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="179">
   <si>
     <t>Timestamp</t>
   </si>
@@ -49,169 +49,169 @@
     <t>Committee Ranking [Foundry]</t>
   </si>
   <si>
-    <t>Please explain your committee rankings. Why are you interested in your top choices?</t>
-  </si>
-  <si>
-    <t>Are there any friends you would like to be placed with? (This is not guaranteed, but we will try our best!)</t>
+    <t>Please use this space to explain your rankings above (prior experience, strong interests, etc). You will be more likely to be assigned your top choices if you do so :)</t>
+  </si>
+  <si>
+    <t>Are there any friends who you want to be in the same committee as?</t>
   </si>
   <si>
     <t>How did you hear about ScottyLabs?</t>
   </si>
   <si>
+    <t>Did you select either Tech or Labrador in your top three options?</t>
+  </si>
+  <si>
     <t>Do you want to answer the Tech committee specific questions?</t>
   </si>
   <si>
-    <t>What is a technical project you are proud of, and what was your role in it?</t>
-  </si>
-  <si>
-    <t>What technologies are you most interested in learning or working with this semester?</t>
+    <t>What's something technical you worked on recently that you're particularly proud of?</t>
+  </si>
+  <si>
+    <t>After looking through the projects page, what team(s)/project(s) stand out most to you? What do you hope to contribute to them?</t>
   </si>
   <si>
     <t>Do you want to answer the Labrador committee specific questions?</t>
   </si>
   <si>
-    <t>Why are you interested in Labrador?</t>
-  </si>
-  <si>
-    <t>What experience do you have with content creation, marketing, or community building?</t>
-  </si>
-  <si>
-    <t>Describe a campus community you have helped grow.</t>
-  </si>
-  <si>
-    <t>What is your favorite ScottyLabs product or event, and how would you promote it?</t>
-  </si>
-  <si>
-    <t>How much time can you commit to Labrador each week?</t>
-  </si>
-  <si>
-    <t>Social media link</t>
-  </si>
-  <si>
-    <t>Github link</t>
-  </si>
-  <si>
-    <t>Anything else you would like the Labrador committee to know?</t>
+    <t>What idea do you want to work on in the committee?</t>
+  </si>
+  <si>
+    <t>Are you interested in a technical role (e.g. backend developer) or a non-technical role (e.g. team lead)? Describe your previous experience in your chosen role type.</t>
+  </si>
+  <si>
+    <t>Why are you excited about Labrador?</t>
+  </si>
+  <si>
+    <t>What makes you a good candidate for the committee?</t>
+  </si>
+  <si>
+    <t>Social media link (personal website, LinkedIn, etc.)</t>
+  </si>
+  <si>
+    <t>Github link (optional: only if technical)</t>
+  </si>
+  <si>
+    <t>Other comments/questions</t>
   </si>
   <si>
     <t>Would you like to answer the Foundry specific questions</t>
   </si>
   <si>
+    <t>What type of membership?</t>
+  </si>
+  <si>
+    <t>Why are you interested in Entrepreneurship?</t>
+  </si>
+  <si>
+    <t>What are you building or hoping to build?</t>
+  </si>
+  <si>
+    <t>Are you looking for cofounders?</t>
+  </si>
+  <si>
+    <t>What have you built, run, or shipped that nobody assigned you? Link it if it exists.</t>
+  </si>
+  <si>
+    <t>LinkedIn (Optional)</t>
+  </si>
+  <si>
+    <t>Website Portfolio (Optional)</t>
+  </si>
+  <si>
+    <t>Would you also like to answer the Foundry analyst member questions?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick your team
-*Note: this is a ranking, so 1st Choice is the team you most want. [Talent]</t>
+*Note: If you mark your interest as an Accelerator team member, you will also be required to give an interview to join the team. [Talent]</t>
   </si>
   <si>
     <t xml:space="preserve">Pick your team
-*Note: this is a ranking, so 1st Choice is the team you most want. [Accelerator]</t>
+*Note: If you mark your interest as an Accelerator team member, you will also be required to give an interview to join the team. [Accelerator]</t>
   </si>
   <si>
     <t xml:space="preserve">Pick your team
-*Note: this is a ranking, so 1st Choice is the team you most want. [Outreach]</t>
-  </si>
-  <si>
-    <t>Why do you want to join Foundry?</t>
-  </si>
-  <si>
-    <t>What does entrepreneurship mean to you?</t>
-  </si>
-  <si>
-    <t>Describe a startup or product you admire and why.</t>
-  </si>
-  <si>
-    <t>Have you ever built or launched something? Tell us about it.</t>
-  </si>
-  <si>
-    <t>What skills would you bring to the Foundry team?</t>
-  </si>
-  <si>
-    <t>How do you handle ambiguity and fast-changing priorities?</t>
-  </si>
-  <si>
-    <t>Describe a time you convinced someone to support an idea.</t>
-  </si>
-  <si>
-    <t>What would you want to change about the CMU startup ecosystem?</t>
-  </si>
-  <si>
-    <t>How many hours per week can you commit to Foundry?</t>
-  </si>
-  <si>
-    <t>Are you interested in the Talent team? If so, why?</t>
-  </si>
-  <si>
-    <t>Are you interested in the Accelerator team? If so, why?</t>
-  </si>
-  <si>
-    <t>Are you interested in the Outreach team? If so, why?</t>
-  </si>
-  <si>
-    <t>Do you have experience with event planning or sponsorship outreach?</t>
-  </si>
-  <si>
-    <t>Anything else you would like the Foundry committee to know?</t>
-  </si>
-  <si>
-    <t>Do you want to answer the Finance committee specific questions?</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [Local Sponsorship]</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [Documentation]</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [University Relations]</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [Purchasing + Planning]</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [Sponsor Relations]</t>
-  </si>
-  <si>
-    <t>Rank your preference for which team you'd like to be in. Please rank from 1 (most preferred) to 6 (least preferred). [Corporate Sponsorship]</t>
-  </si>
-  <si>
-    <t>Why are you interested in the Finance committee?</t>
-  </si>
-  <si>
-    <t>Describe any experience you have with budgeting, sponsorships, or vendor relations.</t>
-  </si>
-  <si>
-    <t>What is your approach to reaching out to a company you have no connection to?</t>
-  </si>
-  <si>
-    <t>Anything else you would like the Finance committee to know?</t>
+*Note: If you mark your interest as an Accelerator team member, you will also be required to give an interview to join the team. [Outreach]</t>
+  </si>
+  <si>
+    <t>Describe your experience with Startups/VC's</t>
+  </si>
+  <si>
+    <t>Pitch us a unique speaker series or event format that would get 100 CMU students in a room who wouldn't otherwise show up.</t>
+  </si>
+  <si>
+    <t>What is a venture capital firm you follow? Describe their investment strategy (thesis) and why you find it interesting.</t>
+  </si>
+  <si>
+    <t>Identify one early-stage startup (Seed or Series A) you believe has high potential. Explain your thesis.</t>
+  </si>
+  <si>
+    <t>Would you also like to answer the Foundry builder member questions?</t>
+  </si>
+  <si>
+    <t>Do you want to apply to our Foundry Builder or Analyst Member?</t>
+  </si>
+  <si>
+    <t>Do you want to answer Finance specific questions?</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [Local Sponsorship]</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [Documentation]</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [University Relations]</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [Purchasing + Planning]</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [Sponsor Relations]</t>
+  </si>
+  <si>
+    <t>Rank your preference for which team you'd like to be in. We will try our best to accommodate everyone into their top choice, but we cannot guarantee placements. [Corporate Sponsorship]</t>
+  </si>
+  <si>
+    <t>Which fruit most represents you and why?</t>
+  </si>
+  <si>
+    <t>Best bad idea you tried?</t>
+  </si>
+  <si>
+    <t>What's your hottest take?</t>
+  </si>
+  <si>
+    <t>Anything else you'd like to share with us? You can leave this blank if you wish.</t>
   </si>
   <si>
     <t>Do you want to answer (not very) Events-specific questions?</t>
   </si>
   <si>
-    <t>What is the best event you have ever attended, and what made it work?</t>
-  </si>
-  <si>
-    <t>If you could run any event on campus, what would it be?</t>
-  </si>
-  <si>
-    <t>Describe a time you had to solve a problem on short notice.</t>
-  </si>
-  <si>
-    <t>How comfortable are you with talking to vendors and campus partners?</t>
-  </si>
-  <si>
-    <t>How many hours per week can you commit to Events?</t>
-  </si>
-  <si>
-    <t>Anything else you would like the Events committee to know?</t>
-  </si>
-  <si>
-    <t>Do you want to answer the Design committee specific questions?</t>
+    <t>Where is Waldo?</t>
+  </si>
+  <si>
+    <t>What's something you did recently you're proud of?</t>
+  </si>
+  <si>
+    <t>What are you adding to the TartanHacks Opening Ceremony playlist?</t>
+  </si>
+  <si>
+    <t>TartanHacks just wrapped up (it's almost midnight). What are you listening to on your way home?</t>
+  </si>
+  <si>
+    <t>Why do you do what you do?</t>
+  </si>
+  <si>
+    <t>If you wrote these questions, what would you do differently?</t>
+  </si>
+  <si>
+    <t>Do you want to answer Design specific questions?</t>
   </si>
   <si>
     <t>What kind of design are you most excited to work on?</t>
   </si>
   <si>
-    <t>Portfolio link</t>
+    <t>Portfolio link (optional but highly recommended!)</t>
   </si>
   <si>
     <t>2026-09-01 09:00:00</t>
@@ -265,7 +265,7 @@
     <t>A campus bus tracker that I wrote the backend for.</t>
   </si>
   <si>
-    <t>TypeScript, Postgres, and anything with a scheduler in it.</t>
+    <t>TartanHacks. I would want to own a slice of the backend.</t>
   </si>
   <si>
     <t>No</t>
@@ -337,7 +337,7 @@
     <t>A terminal client for the campus dining API.</t>
   </si>
   <si>
-    <t>Distributed systems and Rust.</t>
+    <t>The dining API work, since I have already built against it.</t>
   </si>
   <si>
     <t>2026-09-01 09:20:00</t>
@@ -361,19 +361,16 @@
     <t>Instagram</t>
   </si>
   <si>
+    <t>A build-log series that follows one project from kickoff to launch.</t>
+  </si>
+  <si>
+    <t>Non-technical. I ran a club newsletter for two years and edited every issue.</t>
+  </si>
+  <si>
     <t>I want to write about what the other committees ship.</t>
   </si>
   <si>
-    <t>Two years running a club newsletter.</t>
-  </si>
-  <si>
-    <t>Grew a writing circle from four people to thirty.</t>
-  </si>
-  <si>
-    <t>TartanHacks. I would run a build-log series in the weeks before it.</t>
-  </si>
-  <si>
-    <t>About six hours</t>
+    <t>I grew a writing circle from four people to thirty, so I know the slow part.</t>
   </si>
   <si>
     <t>instagram.com/fake.echo.mockworth</t>
@@ -403,46 +400,37 @@
     <t>A poster in Tepper</t>
   </si>
   <si>
-    <t>I want to help students take an idea past the demo stage.</t>
+    <t>Analyst Member</t>
   </si>
   <si>
     <t>Shipping something small to real users, repeatedly.</t>
   </si>
   <si>
-    <t>A local bike-repair co-op that runs entirely on a spreadsheet.</t>
-  </si>
-  <si>
-    <t>A pop-up print shop during finals week.</t>
-  </si>
-  <si>
-    <t>Scheduling, budgets, and cold outreach.</t>
-  </si>
-  <si>
-    <t>I write down the three things that must be true and check them weekly.</t>
-  </si>
-  <si>
-    <t>Convinced a department to fund the print shop by showing the demand.</t>
-  </si>
-  <si>
-    <t>More paths in for people who are not already technical.</t>
-  </si>
-  <si>
-    <t>8-10</t>
-  </si>
-  <si>
-    <t>Yes, I like the recruiting side.</t>
-  </si>
-  <si>
-    <t>Yes, this is my first choice.</t>
-  </si>
-  <si>
-    <t>Somewhat.</t>
-  </si>
-  <si>
-    <t>Ran two department mixers.</t>
-  </si>
-  <si>
-    <t>Available on Fridays.</t>
+    <t>A pop-up print shop that runs during finals week.</t>
+  </si>
+  <si>
+    <t>Not yet</t>
+  </si>
+  <si>
+    <t>The print shop. Nobody asked for it and it broke even.</t>
+  </si>
+  <si>
+    <t>linkedin.com/in/fake-fen-dummyfield</t>
+  </si>
+  <si>
+    <t>https://fake-fen-dummyfield.example.com</t>
+  </si>
+  <si>
+    <t>Two summers at a seed-stage company doing operations.</t>
+  </si>
+  <si>
+    <t>A teardown night where founders show the version that did not work.</t>
+  </si>
+  <si>
+    <t>A fictional seed fund that only backs tools their own portfolio already pays for.</t>
+  </si>
+  <si>
+    <t>An invented campus logistics company; the wedge is the loading dock.</t>
   </si>
   <si>
     <t>2026-09-01 09:33:00</t>
@@ -463,13 +451,13 @@
     <t>Career fair</t>
   </si>
   <si>
-    <t>I want to see how a student org actually funds itself.</t>
-  </si>
-  <si>
-    <t>Treasurer of a 60-person club for a year.</t>
-  </si>
-  <si>
-    <t>Find the person whose job it already is, then be brief.</t>
+    <t>A pomegranate. Disproportionate effort per unit of reward.</t>
+  </si>
+  <si>
+    <t>Treasurer of a 60-person club, on a spreadsheet with no formulas.</t>
+  </si>
+  <si>
+    <t>Most sponsorship decks would work better as a single email.</t>
   </si>
   <si>
     <t>I can send a reference from the club advisor.</t>
@@ -496,22 +484,22 @@
     <t>Activities fair</t>
   </si>
   <si>
-    <t>A midnight breakfast that had exactly enough seating.</t>
-  </si>
-  <si>
-    <t>A campus-wide repair cafe.</t>
+    <t>Behind the catering table, holding the last good coffee.</t>
   </si>
   <si>
     <t>Rebooked a room two hours before an event lost its space.</t>
   </si>
   <si>
-    <t>Very comfortable</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>I have a car, which apparently matters for supply runs.</t>
+    <t>Something with a countable beat so the room starts on time.</t>
+  </si>
+  <si>
+    <t>Whatever was playing when the last team submitted.</t>
+  </si>
+  <si>
+    <t>I would rather run the thing than watch it.</t>
+  </si>
+  <si>
+    <t>I would ask about the worst event, which is more revealing.</t>
   </si>
   <si>
     <t>2026-09-01 09:48:00</t>
@@ -1188,19 +1176,25 @@
       <c r="O2" t="s">
         <v>80</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>82</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>83</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>84</v>
       </c>
       <c r="AB2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2" t="s">
         <v>84</v>
       </c>
       <c r="AT2" t="s">
@@ -1247,13 +1241,19 @@
       <c r="L3" t="s">
         <v>77</v>
       </c>
-      <c r="P3" t="s">
-        <v>84</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="Q3" t="s">
+        <v>84</v>
+      </c>
+      <c r="T3" t="s">
         <v>84</v>
       </c>
       <c r="AB3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR3" t="s">
         <v>84</v>
       </c>
       <c r="AT3" t="s">
@@ -1306,13 +1306,19 @@
       <c r="M4" t="s">
         <v>92</v>
       </c>
-      <c r="P4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="Q4" t="s">
+        <v>84</v>
+      </c>
+      <c r="T4" t="s">
         <v>84</v>
       </c>
       <c r="AB4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR4" t="s">
         <v>84</v>
       </c>
       <c r="AT4" t="s">
@@ -1362,13 +1368,19 @@
       <c r="L5" t="s">
         <v>77</v>
       </c>
-      <c r="P5" t="s">
-        <v>84</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="Q5" t="s">
+        <v>84</v>
+      </c>
+      <c r="T5" t="s">
         <v>84</v>
       </c>
       <c r="AB5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR5" t="s">
         <v>84</v>
       </c>
       <c r="AT5" t="s">
@@ -1424,19 +1436,25 @@
       <c r="O6" t="s">
         <v>105</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>81</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>106</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>107</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>84</v>
       </c>
       <c r="AB6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR6" t="s">
         <v>84</v>
       </c>
       <c r="AT6" t="s">
@@ -1492,37 +1510,40 @@
       <c r="O7" t="s">
         <v>114</v>
       </c>
-      <c r="P7" t="s">
-        <v>84</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="Q7" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" t="s">
         <v>81</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>115</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>116</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>117</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>118</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>119</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>120</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>121</v>
       </c>
-      <c r="AA7" t="s">
-        <v>122</v>
-      </c>
       <c r="AB7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR7" t="s">
         <v>84</v>
       </c>
       <c r="AT7" t="s">
@@ -1537,16 +1558,16 @@
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s">
         <v>123</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>124</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>125</v>
-      </c>
-      <c r="D8" t="s">
-        <v>126</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -1573,70 +1594,70 @@
         <v>71</v>
       </c>
       <c r="M8" t="s">
+        <v>126</v>
+      </c>
+      <c r="O8" t="s">
         <v>127</v>
       </c>
-      <c r="O8" t="s">
-        <v>128</v>
-      </c>
-      <c r="P8" t="s">
-        <v>84</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="Q8" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" t="s">
         <v>84</v>
       </c>
       <c r="AB8" t="s">
         <v>81</v>
       </c>
       <c r="AC8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK8" t="s">
         <v>72</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AL8" t="s">
         <v>71</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AM8" t="s">
         <v>73</v>
       </c>
-      <c r="AF8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>130</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>131</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>132</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL8" t="s">
+      <c r="AN8" t="s">
         <v>135</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AO8" t="s">
         <v>136</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AP8" t="s">
         <v>137</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AQ8" t="s">
         <v>138</v>
       </c>
-      <c r="AP8" t="s">
-        <v>139</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>140</v>
-      </c>
       <c r="AR8" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="AS8" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="AT8" t="s">
         <v>84</v>
@@ -1650,16 +1671,16 @@
     </row>
     <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
         <v>97</v>
@@ -1686,18 +1707,24 @@
         <v>74</v>
       </c>
       <c r="M9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O9" t="s">
-        <v>148</v>
-      </c>
-      <c r="P9" t="s">
-        <v>84</v>
-      </c>
-      <c r="S9" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>84</v>
+      </c>
+      <c r="T9" t="s">
         <v>84</v>
       </c>
       <c r="AB9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR9" t="s">
         <v>84</v>
       </c>
       <c r="AT9" t="s">
@@ -1722,16 +1749,16 @@
         <v>6</v>
       </c>
       <c r="BA9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="BB9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="BC9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="BD9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="BE9" t="s">
         <v>85</v>
@@ -1742,16 +1769,16 @@
     </row>
     <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
         <v>70</v>
@@ -1778,21 +1805,27 @@
         <v>77</v>
       </c>
       <c r="M10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O10" t="s">
-        <v>159</v>
-      </c>
-      <c r="P10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" t="s">
         <v>84</v>
       </c>
       <c r="AB10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR10" t="s">
         <v>84</v>
       </c>
       <c r="AT10" t="s">
@@ -1802,22 +1835,22 @@
         <v>81</v>
       </c>
       <c r="BF10" t="s">
+        <v>156</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>157</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>158</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>159</v>
+      </c>
+      <c r="BJ10" t="s">
         <v>160</v>
       </c>
-      <c r="BG10" t="s">
+      <c r="BK10" t="s">
         <v>161</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>162</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>163</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>164</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>165</v>
       </c>
       <c r="BL10" t="s">
         <v>84</v>
@@ -1825,16 +1858,16 @@
     </row>
     <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>103</v>
@@ -1861,18 +1894,24 @@
         <v>77</v>
       </c>
       <c r="M11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O11" t="s">
-        <v>170</v>
-      </c>
-      <c r="P11" t="s">
-        <v>84</v>
-      </c>
-      <c r="S11" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>84</v>
+      </c>
+      <c r="T11" t="s">
         <v>84</v>
       </c>
       <c r="AB11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR11" t="s">
         <v>84</v>
       </c>
       <c r="AT11" t="s">
@@ -1885,24 +1924,24 @@
         <v>81</v>
       </c>
       <c r="BM11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="BN11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>88</v>
@@ -1929,18 +1968,24 @@
         <v>76</v>
       </c>
       <c r="M12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O12" t="s">
-        <v>178</v>
-      </c>
-      <c r="P12" t="s">
-        <v>84</v>
-      </c>
-      <c r="S12" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T12" t="s">
         <v>84</v>
       </c>
       <c r="AB12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR12" t="s">
         <v>84</v>
       </c>
       <c r="AT12" t="s">
@@ -1955,16 +2000,16 @@
     </row>
     <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F13" t="s">
         <v>71</v>

--- a/apps/server/test/fixtures/fall-2026-sample.xlsx
+++ b/apps/server/test/fixtures/fall-2026-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="179">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1191,12 +1191,6 @@
       <c r="AB2" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>84</v>
-      </c>
       <c r="AT2" t="s">
         <v>84</v>
       </c>
@@ -1250,12 +1244,6 @@
       <c r="AB3" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>84</v>
-      </c>
       <c r="AT3" t="s">
         <v>84</v>
       </c>
@@ -1315,12 +1303,6 @@
       <c r="AB4" t="s">
         <v>84</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>84</v>
-      </c>
       <c r="AT4" t="s">
         <v>84</v>
       </c>
@@ -1377,12 +1359,6 @@
       <c r="AB5" t="s">
         <v>84</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>84</v>
-      </c>
       <c r="AT5" t="s">
         <v>84</v>
       </c>
@@ -1451,12 +1427,6 @@
       <c r="AB6" t="s">
         <v>84</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>84</v>
-      </c>
       <c r="AT6" t="s">
         <v>84</v>
       </c>
@@ -1540,12 +1510,6 @@
       <c r="AB7" t="s">
         <v>84</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>84</v>
-      </c>
       <c r="AT7" t="s">
         <v>84</v>
       </c>
@@ -1721,12 +1685,6 @@
       <c r="AB9" t="s">
         <v>84</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>84</v>
-      </c>
       <c r="AT9" t="s">
         <v>81</v>
       </c>
@@ -1822,12 +1780,6 @@
       <c r="AB10" t="s">
         <v>84</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>84</v>
-      </c>
       <c r="AT10" t="s">
         <v>84</v>
       </c>
@@ -1908,12 +1860,6 @@
       <c r="AB11" t="s">
         <v>84</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>84</v>
-      </c>
       <c r="AT11" t="s">
         <v>84</v>
       </c>
@@ -1980,12 +1926,6 @@
         <v>84</v>
       </c>
       <c r="AB12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR12" t="s">
         <v>84</v>
       </c>
       <c r="AT12" t="s">
